--- a/WorkBot/refactor-experimental/data/transfer_archive/Bakery_Triphammer_20260213.xlsx
+++ b/WorkBot/refactor-experimental/data/transfer_archive/Bakery_Triphammer_20260213.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andrew\Desktop\Andrew\Projects\IthacaBakery\RandomStuff\WorkBot\refactor-experimental\data\transfers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819F548D-5CB0-4CEB-93D7-8706BE68C133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D297CA96-2AF2-4706-9515-D2AA93442FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="3330" windowWidth="16200" windowHeight="9360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Name</t>
   </si>
@@ -55,12 +55,6 @@
     <t>Supplement - Antioxident</t>
   </si>
   <si>
-    <t>Tea Bags - Earl Grey (Twinings)</t>
-  </si>
-  <si>
-    <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
-  </si>
-  <si>
     <t>Tea Bags - English Breakfast (Twinings)</t>
   </si>
   <si>
@@ -79,6 +73,9 @@
     <t>Employee Water</t>
   </si>
   <si>
+    <t>Bindi - Cake Tiramisu Round</t>
+  </si>
+  <si>
     <t>FRZ Fruit - Raspberry (Whole)</t>
   </si>
   <si>
@@ -94,16 +91,16 @@
     <t>Grandma's Coffee Cake - Cranberry</t>
   </si>
   <si>
-    <t>Chobani - Drinkable Yogurt (protein mixed berry)</t>
-  </si>
-  <si>
-    <t>Chobani - Drinkables (Assorted Case)</t>
-  </si>
-  <si>
-    <t>Celsius - Vibe Peach, Tropical, Arctic</t>
-  </si>
-  <si>
-    <t>Java Box (96oz)</t>
+    <t>Flour - Millers Choice</t>
+  </si>
+  <si>
+    <t>Mustard - Honey</t>
+  </si>
+  <si>
+    <t>Container - Plastic Hinged Pie (6")</t>
+  </si>
+  <si>
+    <t>Copy Paper (8.5" x 11")</t>
   </si>
 </sst>
 </file>
@@ -443,10 +440,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -459,7 +457,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -467,15 +465,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -483,7 +481,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -491,23 +489,23 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -515,7 +513,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -523,7 +521,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -531,55 +529,55 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -587,15 +585,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -603,15 +601,15 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -619,53 +617,48 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B26">
+    <sortCondition ref="A2:A26"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>